--- a/top5_jucatori_pozitii.xlsx
+++ b/top5_jucatori_pozitii.xlsx
@@ -442,22 +442,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Saves</t>
+          <t>Save%</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Save%</t>
+          <t>CS_Rate</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>GA90_inv</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>GA90</t>
+          <t>PKsv_Rate</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -472,36 +472,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jean Butez</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="G2" t="n">
-        <v>76.7</v>
+        <v>0.48</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>-0.76</v>
       </c>
       <c r="I2" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9208212659846947</v>
+        <v>0.8719999993650228</v>
       </c>
     </row>
     <row r="3">
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mile Svilar</t>
+          <t>Marco Carnesecchi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,22 +524,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>77.8</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>-0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9026993143298925</v>
+        <v>0.8599628911026269</v>
       </c>
     </row>
     <row r="4">
@@ -565,19 +565,19 @@
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>79.40000000000001</v>
+        <v>0.40625</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>-0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8914815327938421</v>
+        <v>0.8391410230638114</v>
       </c>
     </row>
     <row r="5">
@@ -586,36 +586,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Lucas Chevalier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>79.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>-0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8595512409015365</v>
+        <v>0.8320717124392425</v>
       </c>
     </row>
     <row r="6">
@@ -641,19 +641,19 @@
         <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>78.59999999999999</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8471237346877833</v>
+        <v>0.8289127305503249</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,22 +693,27 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>TklW</t>
+          <t>Def_Actions_90</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>Fls_90</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Fls</t>
+          <t>PlusMinus_90</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Implicare_Defensiva_90</t>
+          <t>Cards_Penalty_90</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Scor_Fundas</t>
         </is>
       </c>
     </row>
@@ -718,12 +723,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanderson</t>
+          <t>Malang Sarr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -732,19 +737,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>1.07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.698972099853157</v>
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7484067802042066</v>
       </c>
     </row>
     <row r="3">
@@ -753,33 +761,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oliver Scarles</t>
+          <t>Kim Min-jae</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West Ham United</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>League</t>
-        </is>
-      </c>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>2.875816993464052</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2.29</v>
       </c>
       <c r="I3" t="n">
-        <v>4.240766073871409</v>
+        <v>0.06535947712418301</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.716975587451517</v>
       </c>
     </row>
     <row r="4">
@@ -788,33 +795,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Maximilian Mittelstädt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Liga</t>
-        </is>
-      </c>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>3.254716981132076</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>0.4716981132075472</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>0.71</v>
       </c>
       <c r="I4" t="n">
-        <v>4.088586030664395</v>
+        <v>0.1415094339622641</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7145821085232631</v>
       </c>
     </row>
     <row r="5">
@@ -823,33 +829,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jan Ziółkowski</t>
+          <t>Eric García</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>3.153846153846154</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>1.192307692307692</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="I5" t="n">
-        <v>3.954802259887006</v>
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6938175070957987</v>
       </c>
     </row>
     <row r="6">
@@ -858,33 +867,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mahamadou Nagida</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>4.090909090909091</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>-0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.933434190620273</v>
+        <v>0.3409090909090909</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6917725390802942</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,20 +936,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Gls</t>
+          <t>Off_Direct_90</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>Def_Actions_90</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>TklW</t>
+          <t>Crs_90</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>PlusMinus_90</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scor_Playmaker</t>
         </is>
@@ -949,33 +966,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bruno Fernandes</t>
+          <t>Michael Olise</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>League</t>
-        </is>
-      </c>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>1.068376068376068</v>
       </c>
       <c r="H2" t="n">
-        <v>31</v>
+        <v>5.555555555555556</v>
       </c>
       <c r="I2" t="n">
-        <v>19.62013098931403</v>
+        <v>2.61</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6519284912242811</v>
       </c>
     </row>
     <row r="3">
@@ -984,29 +1000,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Michael Olise</t>
+          <t>Federico Dimarco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>2.169117647058823</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>9.963235294117647</v>
       </c>
       <c r="I3" t="n">
-        <v>19.06791969243913</v>
+        <v>1.73</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6403633010943689</v>
       </c>
     </row>
     <row r="4">
@@ -1015,33 +1038,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Federico Dimarco</t>
+          <t>Serge Gnabry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>1.037037037037037</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>1.037037037037037</v>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="I4" t="n">
-        <v>16.16832047041529</v>
+        <v>2.51</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.581269525673876</v>
       </c>
     </row>
     <row r="5">
@@ -1063,16 +1085,19 @@
         <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>1.129032258064516</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>1.129032258064516</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="I5" t="n">
-        <v>14.1285771866183</v>
+        <v>2.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5673655097522468</v>
       </c>
     </row>
     <row r="6">
@@ -1081,29 +1106,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Julian Ryerson</t>
+          <t>Lennart Karl</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.6716417910447761</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>1.716417910447761</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>1.865671641791045</v>
       </c>
       <c r="I6" t="n">
-        <v>13.3608634443923</v>
+        <v>2.54</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5589704417372349</v>
       </c>
     </row>
   </sheetData>
@@ -1143,22 +1171,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Gls</t>
+          <t>NonPK_Gls_90</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>Ast_90</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>SoT</t>
+          <t>SoT_Rate</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>G/Sh</t>
+          <t>G_per_SoT</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1173,36 +1201,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Deniz Undav</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>League</t>
-        </is>
-      </c>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>0.2830188679245283</v>
       </c>
       <c r="H2" t="n">
-        <v>51</v>
+        <v>0.3909090909090909</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="J2" t="n">
-        <v>27</v>
+        <v>0.7459167383091525</v>
       </c>
     </row>
     <row r="3">
@@ -1224,19 +1248,19 @@
         <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>0.9401709401709403</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0.2136752136752137</v>
       </c>
       <c r="H3" t="n">
-        <v>62</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="J3" t="n">
-        <v>27</v>
+        <v>0.7236914961206602</v>
       </c>
     </row>
     <row r="4">
@@ -1245,32 +1269,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deniz Undav</t>
+          <t>Pavel Šulc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="H4" t="n">
-        <v>43</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="I4" t="n">
-        <v>0.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>0.6640758576449696</v>
       </c>
     </row>
     <row r="5">
@@ -1296,19 +1324,19 @@
         <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>0.4069767441860465</v>
       </c>
       <c r="I5" t="n">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>0.6410511136034611</v>
       </c>
     </row>
     <row r="6">
@@ -1317,12 +1345,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>João Pedro</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1331,22 +1359,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="H6" t="n">
-        <v>27</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="I6" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>0.6319997157828928</v>
       </c>
     </row>
   </sheetData>

--- a/top5_jucatori_pozitii.xlsx
+++ b/top5_jucatori_pozitii.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Portari" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fundași" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mijlocași" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Atacanți" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fundasi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mijlocasi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Atacanti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,22 +447,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>CS_Rate</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>GA90_inv</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PKsv_Rate</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Scor_Portar</t>
+          <t>Predicted_Save%</t>
         </is>
       </c>
     </row>
@@ -472,36 +457,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Hervé Koffi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
-        <v>79.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8719999993650228</v>
+        <v>79.10022734049384</v>
       </c>
     </row>
     <row r="3">
@@ -510,36 +486,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marco Carnesecchi</t>
+          <t>Mile Svilar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8599628911026269</v>
+        <v>77.40932331861224</v>
       </c>
     </row>
     <row r="4">
@@ -548,36 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mike Maignan</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8391410230638114</v>
+        <v>77.1950676978912</v>
       </c>
     </row>
     <row r="5">
@@ -586,36 +544,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lucas Chevalier</t>
+          <t>Marco Carnesecchi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>72.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8320717124392425</v>
+        <v>77.07714083730536</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +583,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -644,16 +593,7 @@
         <v>78.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8289127305503249</v>
+        <v>76.61114939717369</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,27 +633,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Def_Actions_90</t>
+          <t>+/-90</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Fls_90</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>PlusMinus_90</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Cards_Penalty_90</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Scor_Fundas</t>
+          <t>Predicted_+/-90</t>
         </is>
       </c>
     </row>
@@ -723,36 +648,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Malang Sarr</t>
+          <t>Konrad Laimer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>3.642857142857143</v>
+        <v>3.24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.7484067802042066</v>
+        <v>2.698762914919792</v>
       </c>
     </row>
     <row r="3">
@@ -761,7 +677,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kim Min-jae</t>
+          <t>Dayot Upamecano</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -769,24 +685,19 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>2.875816993464052</v>
+        <v>2.88</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.06535947712418301</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.716975587451517</v>
+        <v>2.599461906066355</v>
       </c>
     </row>
     <row r="4">
@@ -795,32 +706,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maximilian Mittelstädt</t>
+          <t>Josip Stanišić</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>3.254716981132076</v>
+        <v>2.74</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4716981132075472</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.1415094339622641</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.7145821085232631</v>
+        <v>2.531243968575861</v>
       </c>
     </row>
     <row r="5">
@@ -829,36 +735,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eric García</t>
+          <t>Tom Bischof</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>3.153846153846154</v>
+        <v>2.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1.192307692307692</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6938175070957987</v>
+        <v>2.44653584567448</v>
       </c>
     </row>
     <row r="6">
@@ -867,36 +764,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Jonathan Tah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>4.090909090909091</v>
+        <v>2.51</v>
       </c>
       <c r="G6" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.3409090909090909</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6917725390802942</v>
+        <v>2.324695220219583</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,27 +824,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Off_Direct_90</t>
+          <t>G+A</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Def_Actions_90</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Crs_90</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PlusMinus_90</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Scor_Playmaker</t>
+          <t>Predicted_G+A</t>
         </is>
       </c>
     </row>
@@ -974,24 +847,19 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
       <c r="E2" t="n">
         <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>1.282051282051282</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>1.068376068376068</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.555555555555556</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6519284912242811</v>
+        <v>25.7774874575177</v>
       </c>
     </row>
     <row r="3">
@@ -1000,36 +868,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Federico Dimarco</t>
+          <t>Luis Díaz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F3" t="n">
         <v>28</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.7352941176470589</v>
-      </c>
       <c r="G3" t="n">
-        <v>2.169117647058823</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9.963235294117647</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6403633010943689</v>
+        <v>19.37173275945819</v>
       </c>
     </row>
     <row r="4">
@@ -1046,24 +905,19 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>1.037037037037037</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>1.037037037037037</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.555555555555556</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.581269525673876</v>
+        <v>17.84000760424914</v>
       </c>
     </row>
     <row r="5">
@@ -1072,32 +926,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>1.129032258064516</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>1.129032258064516</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.612903225806452</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5673655097522468</v>
+        <v>17.28211009112583</v>
       </c>
     </row>
     <row r="6">
@@ -1106,32 +955,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lennart Karl</t>
+          <t>Marcus Rashford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6716417910447761</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>1.716417910447761</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.865671641791045</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5589704417372349</v>
+        <v>16.79169140813201</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,27 +1015,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NonPK_Gls_90</t>
+          <t>Gls_90</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ast_90</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>SoT_Rate</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>G_per_SoT</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Contributie_Ofensiva</t>
+          <t>Predicted_Gls_90</t>
         </is>
       </c>
     </row>
@@ -1201,32 +1030,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deniz Undav</t>
+          <t>Harry Kane</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.9401709401709403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2830188679245283</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3909090909090909</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.7459167383091525</v>
+        <v>0.9401709401709375</v>
       </c>
     </row>
     <row r="3">
@@ -1235,32 +1059,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Harry Kane</t>
+          <t>Deniz Undav</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9401709401709403</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2136752136752137</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5636363636363636</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7236914961206602</v>
+        <v>0.8490566037735877</v>
       </c>
     </row>
     <row r="4">
@@ -1269,36 +1088,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pavel Šulc</t>
+          <t>Robert Lewandowski</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.8208955223880596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1935483870967742</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3902439024390244</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6640758576449696</v>
+        <v>0.8208955223880604</v>
       </c>
     </row>
     <row r="5">
@@ -1307,36 +1117,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lautaro Martínez</t>
+          <t>Ferrán Torres</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1851851851851852</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.4069767441860465</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6410511136034611</v>
+        <v>0.7523220522010825</v>
       </c>
     </row>
     <row r="6">
@@ -1345,36 +1146,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Lautaro Martínez</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2430555555555556</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.4594594594594595</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6319997157828928</v>
+        <v>0.7408004778972539</v>
       </c>
     </row>
   </sheetData>
